--- a/ig/main/CodeSystem-TRE-A11-IheFormatCode.xlsx
+++ b/ig/main/CodeSystem-TRE-A11-IheFormatCode.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -349,7 +349,7 @@
     <t>urn:ihe:pcc:ips:2020</t>
   </si>
   <si>
-    <t>Synthèse du dossier médical</t>
+    <t>Synthèse médicale</t>
   </si>
   <si>
     <t>urn:ihe:pcc:xds-ms:2007</t>

--- a/ig/main/CodeSystem-TRE-A11-IheFormatCode.xlsx
+++ b/ig/main/CodeSystem-TRE-A11-IheFormatCode.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240426120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/CodeSystem-TRE-A11-IheFormatCode.xlsx
+++ b/ig/main/CodeSystem-TRE-A11-IheFormatCode.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
